--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.02094881690991</v>
+        <v>6.34090418274786</v>
       </c>
       <c r="D2" t="n">
-        <v>39.58990890469885</v>
+        <v>6.433360197013564</v>
       </c>
       <c r="E2" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F2" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.12200481121694</v>
+        <v>6.194825781822753</v>
       </c>
       <c r="D3" t="n">
-        <v>38.37437397346217</v>
+        <v>6.235835770687602</v>
       </c>
       <c r="E3" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F3" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.23830660474413</v>
+        <v>5.888724823270922</v>
       </c>
       <c r="D4" t="n">
-        <v>36.18278282310088</v>
+        <v>5.879702208753893</v>
       </c>
       <c r="E4" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F4" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.91623329991094</v>
+        <v>6.486387911235528</v>
       </c>
       <c r="D5" t="n">
-        <v>39.61184176006617</v>
+        <v>6.436924286010753</v>
       </c>
       <c r="E5" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F5" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.07721615884122</v>
+        <v>4.075047625811699</v>
       </c>
       <c r="D6" t="n">
-        <v>24.65228756642364</v>
+        <v>4.005996729543842</v>
       </c>
       <c r="E6" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F6" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.58757555297819</v>
+        <v>2.695481027358956</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03607957997782</v>
+        <v>2.605862931746396</v>
       </c>
       <c r="E7" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F7" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.5600325728363</v>
+        <v>5.941005293085899</v>
       </c>
       <c r="D8" t="n">
-        <v>35.91830485961172</v>
+        <v>5.836724539686905</v>
       </c>
       <c r="E8" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F8" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.70855198221852</v>
+        <v>5.802639697110509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.4818919073776</v>
+        <v>5.765807434948861</v>
       </c>
       <c r="E9" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F9" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.8612863303668</v>
+        <v>5.664959028684605</v>
       </c>
       <c r="D10" t="n">
-        <v>34.26337860759848</v>
+        <v>5.567799023734754</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F10" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.87501953697257</v>
+        <v>6.479690674758043</v>
       </c>
       <c r="D11" t="n">
-        <v>39.55600704266184</v>
+        <v>6.427851144432549</v>
       </c>
       <c r="E11" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F11" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.09806532001042</v>
+        <v>6.353435614501693</v>
       </c>
       <c r="D12" t="n">
-        <v>38.57099608878031</v>
+        <v>6.267786864426801</v>
       </c>
       <c r="E12" t="n">
-        <v>6.949193342188639</v>
+        <v>1.129243918105654</v>
       </c>
       <c r="F12" t="n">
-        <v>7.08902810961319</v>
+        <v>1.151967067812144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
